--- a/banks/W02_Kahoot匯入.xlsx
+++ b/banks/W02_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>極性</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>解離</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>鹼</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>極性</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>解離</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>水</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -526,30 +526,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>氫鍵</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>熵</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>平衡</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>溶劑</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>氫鍵</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>熵</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -571,12 +571,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>平衡</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>離子鍵</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>平衡</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
@@ -596,30 +596,30 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>熵</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>解離</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>濃度</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>極性</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>熵</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>濃度</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>解離</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -631,30 +631,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>共價鍵</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>氫鍵</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>非極性</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>平衡</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>共價鍵</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>氫鍵</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>非極性</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>離子鍵</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>滴定曲線</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>非極性</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>離子鍵</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -706,25 +706,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>滴定曲線</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>疏水性</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>親水性</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>滴定曲線</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -736,19 +736,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>平衡</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>溶質</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>酸</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>平衡</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>溶劑</t>
@@ -759,7 +759,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -781,20 +781,20 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>平衡</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>溶劑</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -806,30 +806,30 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>濃度</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>氫鍵</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>熵</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>濃度</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>共價鍵</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>氫鍵</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>解離</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>熵</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>解離</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -881,17 +881,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>濃度</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>極性</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>溶劑</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>濃度</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -911,30 +911,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>熵</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>平衡</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>溶劑</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>熵</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>解離</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>平衡</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -946,30 +946,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>溶質</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>解離</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>溶劑</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>平衡</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>解離</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>溶質</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>溶劑</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -981,30 +981,30 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>解離</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>平衡常數</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>滴定曲線</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>離子鍵</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>解離</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1016,30 +1016,30 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>共價鍵</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>疏水性</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>緩衝溶液</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>平衡常數</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>共價鍵</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1051,30 +1051,30 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>共價鍵</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>滴定曲線</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>親水性</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>共價鍵</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>凡德瓦力</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>滴定曲線</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1091,25 +1091,25 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>非極性</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>氫鍵</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>凡德瓦力</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>非極性</t>
-        </is>
-      </c>
       <c r="F19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1121,30 +1121,30 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>解離</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>濃度</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>解離</t>
-        </is>
-      </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>疏水性</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>離子鍵</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>疏水性</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1156,30 +1156,170 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>熵</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>平衡</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>濃度</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>熵</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>平衡</t>
-        </is>
-      </c>
       <c r="F21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:水分子氫鍵) 虛線標號1代表什麼?</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>氫鍵</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>離子鍵</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>共價鍵</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>凡德瓦力</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:pH 滴定曲線) 圖中央那段平緩、pH 變化很小的曲線稱為什麼?</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>當量點</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>緩衝區</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>終點</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>起始點</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>鹼—釋出H⁺</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>疏水性—不溶於水</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>酸—釋出OH⁻</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>親水性—不溶於水</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>[H+]=10⁻³ M,pH=多少?</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
